--- a/docs/培训/OpenWorker培训/02-交期风险/进度跟踪.xlsx
+++ b/docs/培训/OpenWorker培训/02-交期风险/进度跟踪.xlsx
@@ -501,7 +501,7 @@
         <v>55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         <v>95</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>芯轴锻件未到货，供应商答复预计 2026-10-03 到厂</t>
+          <t>芯轴锻件未到货，供应商答复预计 2026-10-08 到厂</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         <v>45</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
         <v>75</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46293</v>
+        <v>46298</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
